--- a/Config/Datas/Tables/x_性能测试_PerformanceScenarioConfig.xlsx
+++ b/Config/Datas/Tables/x_性能测试_PerformanceScenarioConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbPerformanceScenario" sheetId="1" r:id="Rec7ea5b696344ab8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbPerformanceScenario" sheetId="1" r:id="Re867d950d323432a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -62,8 +62,30 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17324D"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF475569"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF1F2937"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="10">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -95,8 +117,23 @@
         <x:fgColor rgb="FF64748B"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF7F9FB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="13">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -176,11 +213,53 @@
         <x:color rgb="FFE5E7EB"/>
       </x:top>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF163A5C"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF163A5C"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF163A5C"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF163A5C"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFCBD5E1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFE5E7EB"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="38">
+  <x:cellXfs count="65">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -290,12 +369,119 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -500,6 +686,25 @@
     <x:col min="5" max="5" width="48" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="48" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="18" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="18" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="18" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="18" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="18" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="18" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="18" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="18" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="18" hidden="0" customWidth="1"/>
+    <x:col min="22" max="22" width="18" hidden="0" customWidth="1"/>
+    <x:col min="23" max="23" width="18" hidden="0" customWidth="1"/>
+    <x:col min="24" max="24" width="18" hidden="0" customWidth="1"/>
+    <x:col min="25" max="25" width="18" hidden="0" customWidth="1"/>
+    <x:col min="26" max="26" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -524,6 +729,63 @@
       <x:c r="G1" s="11" t="str">
         <x:v>entityCount</x:v>
       </x:c>
+      <x:c r="H1" s="44" t="str">
+        <x:v>warmupSeconds</x:v>
+      </x:c>
+      <x:c r="I1" s="44" t="str">
+        <x:v>sampleSeconds</x:v>
+      </x:c>
+      <x:c r="J1" s="44" t="str">
+        <x:v>targetAverageFps</x:v>
+      </x:c>
+      <x:c r="K1" s="44" t="str">
+        <x:v>maxP95FrameTimeMs</x:v>
+      </x:c>
+      <x:c r="L1" s="44" t="str">
+        <x:v>screenWidth</x:v>
+      </x:c>
+      <x:c r="M1" s="44" t="str">
+        <x:v>screenHeight</x:v>
+      </x:c>
+      <x:c r="N1" s="44" t="str">
+        <x:v>spawnColumns</x:v>
+      </x:c>
+      <x:c r="O1" s="44" t="str">
+        <x:v>horizontalSpacing</x:v>
+      </x:c>
+      <x:c r="P1" s="44" t="str">
+        <x:v>verticalSpacing</x:v>
+      </x:c>
+      <x:c r="Q1" s="44" t="str">
+        <x:v>entityScale</x:v>
+      </x:c>
+      <x:c r="R1" s="44" t="str">
+        <x:v>moveAmplitude</x:v>
+      </x:c>
+      <x:c r="S1" s="44" t="str">
+        <x:v>moveSpeedMin</x:v>
+      </x:c>
+      <x:c r="T1" s="44" t="str">
+        <x:v>moveSpeedMax</x:v>
+      </x:c>
+      <x:c r="U1" s="44" t="str">
+        <x:v>randomSeed</x:v>
+      </x:c>
+      <x:c r="V1" s="44" t="str">
+        <x:v>maxGcAllocBytesPerFrame</x:v>
+      </x:c>
+      <x:c r="W1" s="44" t="str">
+        <x:v>cameraPadding</x:v>
+      </x:c>
+      <x:c r="X1" s="44" t="str">
+        <x:v>vSyncCount</x:v>
+      </x:c>
+      <x:c r="Y1" s="44" t="str">
+        <x:v>targetFrameRate</x:v>
+      </x:c>
+      <x:c r="Z1" s="44" t="str">
+        <x:v>runInBackground</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="29" t="str">
@@ -546,6 +808,63 @@
       </x:c>
       <x:c r="G2" s="14" t="str">
         <x:v>int</x:v>
+      </x:c>
+      <x:c r="H2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="I2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="J2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="K2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="L2" s="50" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="M2" s="50" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="N2" s="50" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="O2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="P2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Q2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="R2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="S2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="T2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="U2" s="50" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="V2" s="50" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="W2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="X2" s="50" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="Y2" s="50" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="Z2" s="50" t="str">
+        <x:v>bool</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -558,8 +877,27 @@
       <x:c r="E3" s="16"/>
       <x:c r="F3" s="16"/>
       <x:c r="G3" s="16"/>
+      <x:c r="H3"/>
+      <x:c r="I3"/>
+      <x:c r="J3"/>
+      <x:c r="K3"/>
+      <x:c r="L3"/>
+      <x:c r="M3"/>
+      <x:c r="N3"/>
+      <x:c r="O3"/>
+      <x:c r="P3"/>
+      <x:c r="Q3"/>
+      <x:c r="R3"/>
+      <x:c r="S3"/>
+      <x:c r="T3"/>
+      <x:c r="U3"/>
+      <x:c r="V3"/>
+      <x:c r="W3"/>
+      <x:c r="X3"/>
+      <x:c r="Y3"/>
+      <x:c r="Z3"/>
     </x:row>
-    <x:row r="4" ht="30" customHeight="1">
+    <x:row r="4" ht="42" customHeight="1">
       <x:c r="A4" s="31" t="str">
         <x:v>##</x:v>
       </x:c>
@@ -580,6 +918,63 @@
       </x:c>
       <x:c r="G4" s="24" t="str">
         <x:v>目标同屏实体数量</x:v>
+      </x:c>
+      <x:c r="H4" s="56" t="str">
+        <x:v>预热秒数，预热期间不计入结果</x:v>
+      </x:c>
+      <x:c r="I4" s="56" t="str">
+        <x:v>正式采样秒数</x:v>
+      </x:c>
+      <x:c r="J4" s="56" t="str">
+        <x:v>平均帧率通过线</x:v>
+      </x:c>
+      <x:c r="K4" s="56" t="str">
+        <x:v>P95帧耗时上限，毫秒</x:v>
+      </x:c>
+      <x:c r="L4" s="56" t="str">
+        <x:v>性能测试窗口宽度</x:v>
+      </x:c>
+      <x:c r="M4" s="56" t="str">
+        <x:v>性能测试窗口高度</x:v>
+      </x:c>
+      <x:c r="N4" s="56" t="str">
+        <x:v>实体网格列数</x:v>
+      </x:c>
+      <x:c r="O4" s="56" t="str">
+        <x:v>实体水平间距</x:v>
+      </x:c>
+      <x:c r="P4" s="56" t="str">
+        <x:v>实体垂直间距</x:v>
+      </x:c>
+      <x:c r="Q4" s="56" t="str">
+        <x:v>测试实体渲染缩放</x:v>
+      </x:c>
+      <x:c r="R4" s="56" t="str">
+        <x:v>实体往复移动振幅</x:v>
+      </x:c>
+      <x:c r="S4" s="56" t="str">
+        <x:v>实体最小移动角速度</x:v>
+      </x:c>
+      <x:c r="T4" s="56" t="str">
+        <x:v>实体最大移动角速度</x:v>
+      </x:c>
+      <x:c r="U4" s="56" t="str">
+        <x:v>确定性生成随机种子</x:v>
+      </x:c>
+      <x:c r="V4" s="56" t="str">
+        <x:v>采样期单帧GC分配上限，字节</x:v>
+      </x:c>
+      <x:c r="W4" s="56" t="str">
+        <x:v>正交相机边缘留白</x:v>
+      </x:c>
+      <x:c r="X4" s="56" t="str">
+        <x:v>垂直同步间隔，0表示关闭</x:v>
+      </x:c>
+      <x:c r="Y4" s="56" t="str">
+        <x:v>目标帧率，-1表示不限制</x:v>
+      </x:c>
+      <x:c r="Z4" s="56" t="str">
+        <x:v>失去焦点后是否继续运行</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -600,6 +995,63 @@
       <x:c r="G5" s="35" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H5" s="63" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I5" s="63" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J5" s="63" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K5" s="63" t="n">
+        <x:v>16.67</x:v>
+      </x:c>
+      <x:c r="L5" s="63" t="n">
+        <x:v>1920</x:v>
+      </x:c>
+      <x:c r="M5" s="63" t="n">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="N5" s="63" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="O5" s="63" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P5" s="63" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="Q5" s="63" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="R5" s="63" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="S5" s="63" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="T5" s="63" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="U5" s="63" t="n">
+        <x:v>20260905</x:v>
+      </x:c>
+      <x:c r="V5" s="63" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="W5" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X5" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y5" s="63" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="Z5" s="64" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33"/>
@@ -619,6 +1071,63 @@
       <x:c r="G6" s="36" t="n">
         <x:v>1000</x:v>
       </x:c>
+      <x:c r="H6" s="63" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I6" s="63" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J6" s="63" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K6" s="63" t="n">
+        <x:v>16.67</x:v>
+      </x:c>
+      <x:c r="L6" s="63" t="n">
+        <x:v>1920</x:v>
+      </x:c>
+      <x:c r="M6" s="63" t="n">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="N6" s="63" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="O6" s="63" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P6" s="63" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="Q6" s="63" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="R6" s="63" t="n">
+        <x:v>0.12</x:v>
+      </x:c>
+      <x:c r="S6" s="63" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="T6" s="63" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="U6" s="63" t="n">
+        <x:v>20260905</x:v>
+      </x:c>
+      <x:c r="V6" s="63" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="W6" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X6" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y6" s="63" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="Z6" s="64" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="34"/>
@@ -640,6 +1149,63 @@
       <x:c r="G7" s="37" t="n">
         <x:v>2000</x:v>
       </x:c>
+      <x:c r="H7" s="63" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="I7" s="63" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J7" s="63" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K7" s="63" t="n">
+        <x:v>16.67</x:v>
+      </x:c>
+      <x:c r="L7" s="63" t="n">
+        <x:v>1920</x:v>
+      </x:c>
+      <x:c r="M7" s="63" t="n">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="N7" s="63" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="O7" s="63" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="P7" s="63" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="Q7" s="63" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="R7" s="63" t="n">
+        <x:v>0.1</x:v>
+      </x:c>
+      <x:c r="S7" s="63" t="n">
+        <x:v>0.4</x:v>
+      </x:c>
+      <x:c r="T7" s="63" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="U7" s="63" t="n">
+        <x:v>20260905</x:v>
+      </x:c>
+      <x:c r="V7" s="63" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="W7" s="63" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X7" s="63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y7" s="63" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="Z7" s="64" t="b">
+        <x:v>1</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/Tables/x_性能测试_PerformanceScenarioConfig.xlsx
+++ b/Config/Datas/Tables/x_性能测试_PerformanceScenarioConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbPerformanceScenario" sheetId="1" r:id="Re867d950d323432a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbPerformanceScenario" sheetId="1" r:id="R6fa18da059594ca1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="12">
+  <x:fonts count="18">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -84,8 +84,39 @@
       <x:color rgb="FF1F2937"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="等线"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="等线"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="28">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -130,6 +161,96 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFF7F9FB"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF6F8FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEBF1F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEBF1F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEBF1F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7FA"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -259,7 +380,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="65">
+  <x:cellXfs count="101">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -459,6 +580,112 @@
           <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
         </x:ext>
       </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="13" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="15" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="19" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="21" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="22" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="23" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="20" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="17" fillId="24" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="25" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="26" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="16" fillId="27" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -705,6 +932,22 @@
     <x:col min="24" max="24" width="18" hidden="0" customWidth="1"/>
     <x:col min="25" max="25" width="18" hidden="0" customWidth="1"/>
     <x:col min="26" max="26" width="18" hidden="0" customWidth="1"/>
+    <x:col min="27" max="27" width="24" hidden="0" customWidth="1"/>
+    <x:col min="28" max="28" width="24" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="24" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="24" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="24" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="24" hidden="0" customWidth="1"/>
+    <x:col min="33" max="33" width="24" hidden="0" customWidth="1"/>
+    <x:col min="34" max="34" width="24" hidden="0" customWidth="1"/>
+    <x:col min="35" max="35" width="24" hidden="0" customWidth="1"/>
+    <x:col min="36" max="36" width="24" hidden="0" customWidth="1"/>
+    <x:col min="37" max="37" width="24" hidden="0" customWidth="1"/>
+    <x:col min="38" max="38" width="28" hidden="0" customWidth="1"/>
+    <x:col min="39" max="39" width="34" hidden="0" customWidth="1"/>
+    <x:col min="40" max="40" width="34" hidden="0" customWidth="1"/>
+    <x:col min="41" max="41" width="34" hidden="0" customWidth="1"/>
+    <x:col min="42" max="42" width="34" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -786,6 +1029,54 @@
       <x:c r="Z1" s="44" t="str">
         <x:v>runInBackground</x:v>
       </x:c>
+      <x:c r="AA1" s="70" t="str">
+        <x:v>combatRulesId</x:v>
+      </x:c>
+      <x:c r="AB1" s="70" t="str">
+        <x:v>characterId</x:v>
+      </x:c>
+      <x:c r="AC1" s="70" t="str">
+        <x:v>characterProfileOverrideId</x:v>
+      </x:c>
+      <x:c r="AD1" s="70" t="str">
+        <x:v>monsterProfileOverrideId</x:v>
+      </x:c>
+      <x:c r="AE1" s="70" t="str">
+        <x:v>arenaHalfWidth</x:v>
+      </x:c>
+      <x:c r="AF1" s="70" t="str">
+        <x:v>arenaHalfHeight</x:v>
+      </x:c>
+      <x:c r="AG1" s="70" t="str">
+        <x:v>playerStartX</x:v>
+      </x:c>
+      <x:c r="AH1" s="70" t="str">
+        <x:v>playerStartY</x:v>
+      </x:c>
+      <x:c r="AI1" s="70" t="str">
+        <x:v>replenishOnDeath</x:v>
+      </x:c>
+      <x:c r="AJ1" s="70" t="str">
+        <x:v>playerHealthPolicy</x:v>
+      </x:c>
+      <x:c r="AK1" s="70" t="str">
+        <x:v>playerInputPolicy</x:v>
+      </x:c>
+      <x:c r="AL1" s="80" t="str">
+        <x:v>presentationId</x:v>
+      </x:c>
+      <x:c r="AM1" s="97" t="str">
+        <x:v>spawnRadiusPixels</x:v>
+      </x:c>
+      <x:c r="AN1" s="97" t="str">
+        <x:v>spawnIntervalSeconds</x:v>
+      </x:c>
+      <x:c r="AO1" s="97" t="str">
+        <x:v>spawnBatchCount</x:v>
+      </x:c>
+      <x:c r="AP1" s="97" t="str">
+        <x:v>spawnUnitIntervalSeconds</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="29" t="str">
@@ -865,6 +1156,54 @@
       </x:c>
       <x:c r="Z2" s="50" t="str">
         <x:v>bool</x:v>
+      </x:c>
+      <x:c r="AA2" s="72" t="str">
+        <x:v>int?#ref=TbCombatRules</x:v>
+      </x:c>
+      <x:c r="AB2" s="72" t="str">
+        <x:v>int?#ref=TbCharacter</x:v>
+      </x:c>
+      <x:c r="AC2" s="72" t="str">
+        <x:v>int?#ref=TbAttributeProfile</x:v>
+      </x:c>
+      <x:c r="AD2" s="72" t="str">
+        <x:v>int?#ref=TbAttributeProfile</x:v>
+      </x:c>
+      <x:c r="AE2" s="72" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="AF2" s="72" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="AG2" s="72" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="AH2" s="72" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="AI2" s="72" t="str">
+        <x:v>bool?</x:v>
+      </x:c>
+      <x:c r="AJ2" s="72" t="str">
+        <x:v>ETestHealthPolicy?</x:v>
+      </x:c>
+      <x:c r="AK2" s="72" t="str">
+        <x:v>ETestInputPolicy?</x:v>
+      </x:c>
+      <x:c r="AL2" s="81" t="str">
+        <x:v>int?#ref=TbCombatPresentation</x:v>
+      </x:c>
+      <x:c r="AM2" s="98" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="AN2" s="98" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="AO2" s="98" t="str">
+        <x:v>int?</x:v>
+      </x:c>
+      <x:c r="AP2" s="98" t="str">
+        <x:v>float?</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -896,8 +1235,24 @@
       <x:c r="X3"/>
       <x:c r="Y3"/>
       <x:c r="Z3"/>
+      <x:c r="AA3" s="73"/>
+      <x:c r="AB3" s="73"/>
+      <x:c r="AC3" s="73"/>
+      <x:c r="AD3" s="73"/>
+      <x:c r="AE3" s="73"/>
+      <x:c r="AF3" s="73"/>
+      <x:c r="AG3" s="73"/>
+      <x:c r="AH3" s="73"/>
+      <x:c r="AI3" s="73"/>
+      <x:c r="AJ3" s="73"/>
+      <x:c r="AK3" s="73"/>
+      <x:c r="AL3" s="78"/>
+      <x:c r="AM3" s="99"/>
+      <x:c r="AN3" s="99"/>
+      <x:c r="AO3" s="99"/>
+      <x:c r="AP3" s="99"/>
     </x:row>
-    <x:row r="4" ht="42" customHeight="1">
+    <x:row r="4" ht="70" customHeight="1">
       <x:c r="A4" s="31" t="str">
         <x:v>##</x:v>
       </x:c>
@@ -975,6 +1330,54 @@
       </x:c>
       <x:c r="Z4" s="56" t="str">
         <x:v>失去焦点后是否继续运行</x:v>
+      </x:c>
+      <x:c r="AA4" s="74" t="str">
+        <x:v>Combat规则；旧移动基准留空</x:v>
+      </x:c>
+      <x:c r="AB4" s="74" t="str">
+        <x:v>测试玩家ID</x:v>
+      </x:c>
+      <x:c r="AC4" s="74" t="str">
+        <x:v>显式测试属性替换；非正式成长</x:v>
+      </x:c>
+      <x:c r="AD4" s="74" t="str">
+        <x:v>显式测试怪物属性替换</x:v>
+      </x:c>
+      <x:c r="AE4" s="74" t="str">
+        <x:v>开放场地半宽，世界单位</x:v>
+      </x:c>
+      <x:c r="AF4" s="74" t="str">
+        <x:v>开放场地半高，世界单位</x:v>
+      </x:c>
+      <x:c r="AG4" s="74" t="str">
+        <x:v>玩家出生X</x:v>
+      </x:c>
+      <x:c r="AH4" s="74" t="str">
+        <x:v>玩家出生Y</x:v>
+      </x:c>
+      <x:c r="AI4" s="74" t="str">
+        <x:v>当tick死亡怪物回收后补齐</x:v>
+      </x:c>
+      <x:c r="AJ4" s="74" t="str">
+        <x:v>RestoreAfterDamage仅供压力测试</x:v>
+      </x:c>
+      <x:c r="AK4" s="74" t="str">
+        <x:v>Stationary为固定玩家输入；手动为闭环测试</x:v>
+      </x:c>
+      <x:c r="AL4" s="78" t="str">
+        <x:v>Combat表现方案；旧基准留空</x:v>
+      </x:c>
+      <x:c r="AM4" s="100" t="str">
+        <x:v>跟随角色圆周出生半径，逻辑像素；空表示旧阵列</x:v>
+      </x:c>
+      <x:c r="AN4" s="100" t="str">
+        <x:v>波间等待秒数；上一波最后一只之后计时，首波同样等待</x:v>
+      </x:c>
+      <x:c r="AO4" s="100" t="str">
+        <x:v>每波只数；不设存活上限，死亡槽复用</x:v>
+      </x:c>
+      <x:c r="AP4" s="100" t="str">
+        <x:v>波内每只生成间隔，模拟秒</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1052,6 +1455,22 @@
       <x:c r="Z5" s="64" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AA5" s="68"/>
+      <x:c r="AB5" s="68"/>
+      <x:c r="AC5" s="68"/>
+      <x:c r="AD5" s="68"/>
+      <x:c r="AE5" s="68"/>
+      <x:c r="AF5" s="68"/>
+      <x:c r="AG5" s="68"/>
+      <x:c r="AH5" s="68"/>
+      <x:c r="AI5" s="68"/>
+      <x:c r="AJ5" s="68"/>
+      <x:c r="AK5" s="68"/>
+      <x:c r="AL5" s="78"/>
+      <x:c r="AM5" s="84"/>
+      <x:c r="AN5" s="84"/>
+      <x:c r="AO5" s="84"/>
+      <x:c r="AP5" s="84"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33"/>
@@ -1128,6 +1547,22 @@
       <x:c r="Z6" s="64" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AA6" s="68"/>
+      <x:c r="AB6" s="68"/>
+      <x:c r="AC6" s="68"/>
+      <x:c r="AD6" s="68"/>
+      <x:c r="AE6" s="68"/>
+      <x:c r="AF6" s="68"/>
+      <x:c r="AG6" s="68"/>
+      <x:c r="AH6" s="68"/>
+      <x:c r="AI6" s="68"/>
+      <x:c r="AJ6" s="68"/>
+      <x:c r="AK6" s="68"/>
+      <x:c r="AL6" s="78"/>
+      <x:c r="AM6" s="84"/>
+      <x:c r="AN6" s="84"/>
+      <x:c r="AO6" s="84"/>
+      <x:c r="AP6" s="84"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="34"/>
@@ -1206,6 +1641,266 @@
       <x:c r="Z7" s="64" t="b">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="AA7" s="68"/>
+      <x:c r="AB7" s="68"/>
+      <x:c r="AC7" s="68"/>
+      <x:c r="AD7" s="68"/>
+      <x:c r="AE7" s="68"/>
+      <x:c r="AF7" s="68"/>
+      <x:c r="AG7" s="68"/>
+      <x:c r="AH7" s="68"/>
+      <x:c r="AI7" s="68"/>
+      <x:c r="AJ7" s="68"/>
+      <x:c r="AK7" s="68"/>
+      <x:c r="AL7" s="78"/>
+      <x:c r="AM7" s="84"/>
+      <x:c r="AN7" s="84"/>
+      <x:c r="AO7" s="84"/>
+      <x:c r="AP7" s="84"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8"/>
+      <x:c r="B8" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" t="str">
+        <x:v>基础战斗闭环</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>Combat</x:v>
+      </x:c>
+      <x:c r="E8" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="F8" t="str">
+        <x:v>20001;20002</x:v>
+      </x:c>
+      <x:c r="G8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H8" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I8" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J8" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K8" t="n">
+        <x:v>16.67</x:v>
+      </x:c>
+      <x:c r="L8" t="n">
+        <x:v>1920</x:v>
+      </x:c>
+      <x:c r="M8" t="n">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="N8" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="O8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P8" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="Q8" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="R8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U8" t="n">
+        <x:v>20260905</x:v>
+      </x:c>
+      <x:c r="V8" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="W8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y8" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="Z8" s="38" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB8" t="n">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="AC8" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AD8" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AE8" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="AF8" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="AG8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI8" s="38" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AJ8" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="AK8" t="str">
+        <x:v>Manual</x:v>
+      </x:c>
+      <x:c r="AL8" s="78" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM8" s="84" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="AN8" s="84" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AO8" s="84" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="AP8" s="84" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9"/>
+      <x:c r="B9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>千怪概率战斗压测</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Combat</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>20001;20002</x:v>
+      </x:c>
+      <x:c r="G9" t="n">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="H9" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I9" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="J9" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="K9" t="n">
+        <x:v>16.67</x:v>
+      </x:c>
+      <x:c r="L9" t="n">
+        <x:v>1920</x:v>
+      </x:c>
+      <x:c r="M9" t="n">
+        <x:v>1080</x:v>
+      </x:c>
+      <x:c r="N9" t="n">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="O9" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="P9" t="n">
+        <x:v>0.55</x:v>
+      </x:c>
+      <x:c r="Q9" t="n">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="R9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="T9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U9" t="n">
+        <x:v>20260905</x:v>
+      </x:c>
+      <x:c r="V9" t="n">
+        <x:v>1024</x:v>
+      </x:c>
+      <x:c r="W9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="X9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="Y9" t="n">
+        <x:v>-1</x:v>
+      </x:c>
+      <x:c r="Z9" s="38" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AA9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AB9" t="n">
+        <x:v>10001</x:v>
+      </x:c>
+      <x:c r="AC9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="AD9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="AE9" t="n">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="AF9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="AG9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AH9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="AI9" s="38" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AJ9" t="str">
+        <x:v>RestoreAfterDamage</x:v>
+      </x:c>
+      <x:c r="AK9" t="str">
+        <x:v>Stationary</x:v>
+      </x:c>
+      <x:c r="AL9" s="78" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AM9" s="84"/>
+      <x:c r="AN9" s="84"/>
+      <x:c r="AO9" s="84"/>
+      <x:c r="AP9" s="84"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/Tables/x_性能测试_PerformanceScenarioConfig.xlsx
+++ b/Config/Datas/Tables/x_性能测试_PerformanceScenarioConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbPerformanceScenario" sheetId="1" r:id="Rc1479e38b6fc43d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbPerformanceScenario" sheetId="1" r:id="R06ff4880efbd4b35"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1002,25 +1002,19 @@
       <x:c r="N1" s="44" t="str">
         <x:v>spawnColumns</x:v>
       </x:c>
-      <x:c r="O1" s="44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">horizontalSpacingMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P1" s="44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">verticalSpacingMilli</x:t>
-        </x:is>
+      <x:c r="O1" s="44" t="str">
+        <x:v>horizontalSpacingPixels</x:v>
+      </x:c>
+      <x:c r="P1" s="44" t="str">
+        <x:v>verticalSpacingPixels</x:v>
       </x:c>
       <x:c r="Q1" s="44" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">entityScaleMilli</x:t>
         </x:is>
       </x:c>
-      <x:c r="R1" s="44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">moveAmplitudeMilli</x:t>
-        </x:is>
+      <x:c r="R1" s="44" t="str">
+        <x:v>moveAmplitudePixels</x:v>
       </x:c>
       <x:c r="S1" s="44" t="inlineStr">
         <x:is>
@@ -1038,10 +1032,8 @@
       <x:c r="V1" s="44" t="str">
         <x:v>maxGcAllocBytesPerFrame</x:v>
       </x:c>
-      <x:c r="W1" s="44" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">cameraPaddingMilli</x:t>
-        </x:is>
+      <x:c r="W1" s="44" t="str">
+        <x:v>cameraPaddingPixels</x:v>
       </x:c>
       <x:c r="X1" s="44" t="str">
         <x:v>vSyncCount</x:v>
@@ -1064,25 +1056,17 @@
       <x:c r="AD1" s="70" t="str">
         <x:v>monsterProfileOverrideId</x:v>
       </x:c>
-      <x:c r="AE1" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">arenaHalfWidthMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AF1" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">arenaHalfHeightMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AG1" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">playerStartXMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AH1" s="70" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">playerStartYMilli</x:t>
-        </x:is>
+      <x:c r="AE1" s="70" t="str">
+        <x:v>arenaHalfWidthPixels</x:v>
+      </x:c>
+      <x:c r="AF1" s="70" t="str">
+        <x:v>arenaHalfHeightPixels</x:v>
+      </x:c>
+      <x:c r="AG1" s="70" t="str">
+        <x:v>playerStartXPixels</x:v>
+      </x:c>
+      <x:c r="AH1" s="70" t="str">
+        <x:v>playerStartYPixels</x:v>
       </x:c>
       <x:c r="AI1" s="70" t="str">
         <x:v>replenishOnDeath</x:v>
@@ -1096,10 +1080,8 @@
       <x:c r="AL1" s="80" t="str">
         <x:v>presentationId</x:v>
       </x:c>
-      <x:c r="AM1" s="97" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">spawnRadiusPixelsMilli</x:t>
-        </x:is>
+      <x:c r="AM1" s="97" t="str">
+        <x:v>spawnRadiusPixels</x:v>
       </x:c>
       <x:c r="AN1" s="97" t="inlineStr">
         <x:is>
@@ -1169,25 +1151,19 @@
       <x:c r="N2" s="50" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="O2" s="50" t="inlineStr">
+      <x:c r="O2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="P2" s="50" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="Q2" s="50" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">int</x:t>
         </x:is>
       </x:c>
-      <x:c r="P2" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="Q2" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="R2" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
+      <x:c r="R2" s="50" t="str">
+        <x:v>float</x:v>
       </x:c>
       <x:c r="S2" s="50" t="inlineStr">
         <x:is>
@@ -1205,10 +1181,8 @@
       <x:c r="V2" s="50" t="str">
         <x:v>int</x:v>
       </x:c>
-      <x:c r="W2" s="50" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int</x:t>
-        </x:is>
+      <x:c r="W2" s="50" t="str">
+        <x:v>float</x:v>
       </x:c>
       <x:c r="X2" s="50" t="str">
         <x:v>int</x:v>
@@ -1220,7 +1194,7 @@
         <x:v>bool</x:v>
       </x:c>
       <x:c r="AA2" s="72" t="str">
-        <x:v>int?#ref=TbCombatRules</x:v>
+        <x:v>int#ref=TbCombatRules</x:v>
       </x:c>
       <x:c r="AB2" s="72" t="str">
         <x:v>int?#ref=TbCharacter</x:v>
@@ -1231,25 +1205,17 @@
       <x:c r="AD2" s="72" t="str">
         <x:v>int?#ref=TbAttributeProfile</x:v>
       </x:c>
-      <x:c r="AE2" s="72" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AF2" s="72" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AG2" s="72" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AH2" s="72" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?</x:t>
-        </x:is>
+      <x:c r="AE2" s="72" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="AF2" s="72" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="AG2" s="72" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="AH2" s="72" t="str">
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="AI2" s="72" t="str">
         <x:v>bool?</x:v>
@@ -1263,10 +1229,8 @@
       <x:c r="AL2" s="81" t="str">
         <x:v>int?#ref=TbCombatPresentation</x:v>
       </x:c>
-      <x:c r="AM2" s="98" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">int?</x:t>
-        </x:is>
+      <x:c r="AM2" s="98" t="str">
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="AN2" s="98" t="inlineStr">
         <x:is>
@@ -1383,25 +1347,19 @@
       <x:c r="N4" s="56" t="str">
         <x:v>实体网格列数</x:v>
       </x:c>
-      <x:c r="O4" s="56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">实体水平间距；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="P4" s="56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">实体垂直间距；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
+      <x:c r="O4" s="56" t="str">
+        <x:v>实体水平间距，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="P4" s="56" t="str">
+        <x:v>实体垂直间距，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="Q4" s="56" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">测试实体渲染缩放；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
         </x:is>
       </x:c>
-      <x:c r="R4" s="56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">实体往复移动振幅；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
+      <x:c r="R4" s="56" t="str">
+        <x:v>实体往复移动振幅，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="S4" s="56" t="inlineStr">
         <x:is>
@@ -1419,10 +1377,8 @@
       <x:c r="V4" s="56" t="str">
         <x:v>采样期单帧GC分配上限，字节</x:v>
       </x:c>
-      <x:c r="W4" s="56" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">正交相机边缘留白；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
+      <x:c r="W4" s="56" t="str">
+        <x:v>正交相机边缘留白，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="X4" s="56" t="str">
         <x:v>垂直同步间隔，0表示关闭</x:v>
@@ -1434,7 +1390,7 @@
         <x:v>失去焦点后是否继续运行</x:v>
       </x:c>
       <x:c r="AA4" s="74" t="str">
-        <x:v>Combat规则；旧移动基准留空</x:v>
+        <x:v>像素到世界单位比例；全部场景必填，引用TbCombatRules。</x:v>
       </x:c>
       <x:c r="AB4" s="74" t="str">
         <x:v>测试玩家ID</x:v>
@@ -1445,25 +1401,17 @@
       <x:c r="AD4" s="74" t="str">
         <x:v>显式测试怪物属性替换</x:v>
       </x:c>
-      <x:c r="AE4" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">开放场地半宽，世界单位；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AF4" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">开放场地半高，世界单位；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AG4" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玩家出生X；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="AH4" s="74" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">玩家出生Y；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
+      <x:c r="AE4" s="74" t="str">
+        <x:v>开放场地半宽，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="AF4" s="74" t="str">
+        <x:v>开放场地半高，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="AG4" s="74" t="str">
+        <x:v>玩家出生X，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="AH4" s="74" t="str">
+        <x:v>玩家出生Y，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="AI4" s="74" t="str">
         <x:v>当tick死亡怪物回收后补齐</x:v>
@@ -1477,10 +1425,8 @@
       <x:c r="AL4" s="78" t="str">
         <x:v>Combat表现方案；旧基准留空</x:v>
       </x:c>
-      <x:c r="AM4" s="100" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">跟随角色圆周出生半径，逻辑像素；空表示旧阵列；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
+      <x:c r="AM4" s="100" t="str">
+        <x:v>跟随角色圆周出生半径；空表示不启用圆周出生，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="AN4" s="100" t="inlineStr">
         <x:is>
@@ -1538,17 +1484,17 @@
       <x:c r="N5" s="63" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="O5" s="63">
-        <x:v>550</x:v>
-      </x:c>
-      <x:c r="P5" s="63">
-        <x:v>550</x:v>
+      <x:c r="O5" s="63" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="P5" s="63" t="n">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q5" s="63">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="R5" s="63">
-        <x:v>120</x:v>
+      <x:c r="R5" s="63" t="n">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="S5" s="63">
         <x:v>400</x:v>
@@ -1562,8 +1508,8 @@
       <x:c r="V5" s="63" t="n">
         <x:v>1024</x:v>
       </x:c>
-      <x:c r="W5" s="63">
-        <x:v>1000</x:v>
+      <x:c r="W5" s="63" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="X5" s="63" t="n">
         <x:v>0</x:v>
@@ -1574,7 +1520,9 @@
       <x:c r="Z5" s="64" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AA5" s="68"/>
+      <x:c r="AA5" s="68" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="AB5" s="68"/>
       <x:c r="AC5" s="68"/>
       <x:c r="AD5" s="68"/>
@@ -1631,17 +1579,17 @@
       <x:c r="N6" s="63" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="O6" s="63">
-        <x:v>550</x:v>
-      </x:c>
-      <x:c r="P6" s="63">
-        <x:v>550</x:v>
+      <x:c r="O6" s="63" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="P6" s="63" t="n">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q6" s="63">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="R6" s="63">
-        <x:v>120</x:v>
+      <x:c r="R6" s="63" t="n">
+        <x:v>12</x:v>
       </x:c>
       <x:c r="S6" s="63">
         <x:v>400</x:v>
@@ -1655,8 +1603,8 @@
       <x:c r="V6" s="63" t="n">
         <x:v>1024</x:v>
       </x:c>
-      <x:c r="W6" s="63">
-        <x:v>1000</x:v>
+      <x:c r="W6" s="63" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="X6" s="63" t="n">
         <x:v>0</x:v>
@@ -1667,7 +1615,9 @@
       <x:c r="Z6" s="64" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AA6" s="68"/>
+      <x:c r="AA6" s="68" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="AB6" s="68"/>
       <x:c r="AC6" s="68"/>
       <x:c r="AD6" s="68"/>
@@ -1726,17 +1676,17 @@
       <x:c r="N7" s="63" t="n">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="O7" s="63">
-        <x:v>500</x:v>
-      </x:c>
-      <x:c r="P7" s="63">
-        <x:v>500</x:v>
+      <x:c r="O7" s="63" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="P7" s="63" t="n">
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q7" s="63">
         <x:v>400</x:v>
       </x:c>
-      <x:c r="R7" s="63">
-        <x:v>100</x:v>
+      <x:c r="R7" s="63" t="n">
+        <x:v>10</x:v>
       </x:c>
       <x:c r="S7" s="63">
         <x:v>400</x:v>
@@ -1750,8 +1700,8 @@
       <x:c r="V7" s="63" t="n">
         <x:v>1024</x:v>
       </x:c>
-      <x:c r="W7" s="63">
-        <x:v>1000</x:v>
+      <x:c r="W7" s="63" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="X7" s="63" t="n">
         <x:v>0</x:v>
@@ -1762,7 +1712,9 @@
       <x:c r="Z7" s="64" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AA7" s="68"/>
+      <x:c r="AA7" s="68" t="n">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="AB7" s="68"/>
       <x:c r="AC7" s="68"/>
       <x:c r="AD7" s="68"/>
@@ -1821,16 +1773,16 @@
       <x:c r="N8" t="n">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="O8">
-        <x:v>550</x:v>
-      </x:c>
-      <x:c r="P8">
-        <x:v>550</x:v>
+      <x:c r="O8" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="P8" t="n">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q8">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="R8">
+      <x:c r="R8" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="S8">
@@ -1845,8 +1797,8 @@
       <x:c r="V8" t="n">
         <x:v>1024</x:v>
       </x:c>
-      <x:c r="W8">
-        <x:v>1000</x:v>
+      <x:c r="W8" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="X8" t="n">
         <x:v>0</x:v>
@@ -1869,16 +1821,16 @@
       <x:c r="AD8" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="AE8">
-        <x:v>12000</x:v>
-      </x:c>
-      <x:c r="AF8">
-        <x:v>8000</x:v>
-      </x:c>
-      <x:c r="AG8">
+      <x:c r="AE8" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="AF8" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="AG8" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AH8">
+      <x:c r="AH8" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI8" s="38" t="b">
@@ -1893,8 +1845,8 @@
       <x:c r="AL8" s="78" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AM8" s="84">
-        <x:v>1000000</x:v>
+      <x:c r="AM8" s="84" t="n">
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="AN8" s="84">
         <x:v>1000</x:v>
@@ -1950,16 +1902,16 @@
       <x:c r="N9" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="O9">
-        <x:v>550</x:v>
-      </x:c>
-      <x:c r="P9">
-        <x:v>550</x:v>
+      <x:c r="O9" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="P9" t="n">
+        <x:v>55</x:v>
       </x:c>
       <x:c r="Q9">
         <x:v>450</x:v>
       </x:c>
-      <x:c r="R9">
+      <x:c r="R9" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="S9">
@@ -1974,8 +1926,8 @@
       <x:c r="V9" t="n">
         <x:v>1024</x:v>
       </x:c>
-      <x:c r="W9">
-        <x:v>1000</x:v>
+      <x:c r="W9" t="n">
+        <x:v>100</x:v>
       </x:c>
       <x:c r="X9" t="n">
         <x:v>0</x:v>
@@ -1998,16 +1950,16 @@
       <x:c r="AD9" t="n">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="AE9">
-        <x:v>12000</x:v>
-      </x:c>
-      <x:c r="AF9">
-        <x:v>8000</x:v>
-      </x:c>
-      <x:c r="AG9">
+      <x:c r="AE9" t="n">
+        <x:v>1200</x:v>
+      </x:c>
+      <x:c r="AF9" t="n">
+        <x:v>800</x:v>
+      </x:c>
+      <x:c r="AG9" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="AH9">
+      <x:c r="AH9" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="AI9" s="38" t="b">
